--- a/SplitFlapDriverATtiny1616 V2 KiCad/Fabrication Files/CPL File.xlsx
+++ b/SplitFlapDriverATtiny1616 V2 KiCad/Fabrication Files/CPL File.xlsx
@@ -1,21 +1,34 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gordo\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gordo\Documents\SplitFlapDisplay\SplitFlapDriverATtiny1616 V2 KiCad\Fabrication Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DDBA0DE0-7EC3-4EF4-BC1F-C1DED4001551}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6C2BCE4-7114-47C7-8629-63FAC55BDCC3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-38510" yWindow="-110" windowWidth="38620" windowHeight="21220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-29670" yWindow="5470" windowWidth="21600" windowHeight="11390" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="144525"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -34,7 +47,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="31">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="43" uniqueCount="25">
   <si>
     <t>Designator</t>
   </si>
@@ -69,12 +82,6 @@
     <t>C6</t>
   </si>
   <si>
-    <t>J1</t>
-  </si>
-  <si>
-    <t>J2</t>
-  </si>
-  <si>
     <t>J3</t>
   </si>
   <si>
@@ -99,9 +106,6 @@
     <t>C7</t>
   </si>
   <si>
-    <t>J5</t>
-  </si>
-  <si>
     <t>top</t>
   </si>
   <si>
@@ -112,15 +116,6 @@
   </si>
   <si>
     <t>D1</t>
-  </si>
-  <si>
-    <t>J6</t>
-  </si>
-  <si>
-    <t>J7</t>
-  </si>
-  <si>
-    <t>J8</t>
   </si>
   <si>
     <t>R2</t>
@@ -169,7 +164,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -207,17 +202,6 @@
     </border>
     <border>
       <left/>
-      <right/>
-      <top style="thin">
-        <color theme="9" tint="0.39997558519241921"/>
-      </top>
-      <bottom style="thin">
-        <color theme="9" tint="0.39997558519241921"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color theme="9" tint="0.39997558519241921"/>
       </right>
@@ -235,31 +219,26 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="3" xfId="0" applyFill="1" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -535,7 +514,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E26"/>
+  <dimension ref="A1:E20"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="13.5703125" customWidth="1"/>
@@ -563,428 +542,327 @@
       </c>
     </row>
     <row r="2" spans="1:5">
-      <c r="A2" s="4" t="s">
+      <c r="A2" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="2">
+      <c r="B2" s="6">
         <v>143.77500000000001</v>
       </c>
-      <c r="C2" s="2">
+      <c r="C2" s="6">
         <v>-121.3</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E2" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:5">
+      <c r="A3" s="3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" s="6">
+        <v>138.4</v>
+      </c>
+      <c r="C3" s="6">
+        <v>-102.35</v>
+      </c>
+      <c r="D3" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E3" s="6">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="B4" s="6">
+        <v>125.5625</v>
+      </c>
+      <c r="C4" s="6">
+        <v>-120.8875</v>
+      </c>
+      <c r="D4" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E4" s="6">
+        <v>-90</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="B5" s="6">
+        <v>127.0625</v>
+      </c>
+      <c r="C5" s="6">
+        <v>-120.8875</v>
+      </c>
+      <c r="D5" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E5" s="6">
+        <v>-90</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="B6" s="6">
+        <v>124.6</v>
+      </c>
+      <c r="C6" s="6">
+        <v>-109.75</v>
+      </c>
+      <c r="D6" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E6" s="6">
+        <v>-90</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="B7" s="6">
+        <v>129.55000000000001</v>
+      </c>
+      <c r="C7" s="6">
+        <v>-109.72499999999999</v>
+      </c>
+      <c r="D7" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="6">
+        <v>-90</v>
+      </c>
+    </row>
+    <row r="8" spans="1:5">
+      <c r="A8" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="B8" s="6">
+        <v>128.5625</v>
+      </c>
+      <c r="C8" s="6">
+        <v>-120.8875</v>
+      </c>
+      <c r="D8" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E8" s="6">
+        <v>-90</v>
+      </c>
+    </row>
+    <row r="9" spans="1:5">
+      <c r="A9" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="B9" s="6">
+        <v>129.53749999999999</v>
+      </c>
+      <c r="C9" s="6">
+        <v>-114.58750000000001</v>
+      </c>
+      <c r="D9" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E9" s="6">
+        <v>-90</v>
+      </c>
+    </row>
+    <row r="10" spans="1:5">
+      <c r="A10" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="B10" s="6">
+        <v>124.5625</v>
+      </c>
+      <c r="C10" s="6">
+        <v>-114.6125</v>
+      </c>
+      <c r="D10" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E10" s="6">
+        <v>-90</v>
+      </c>
+    </row>
+    <row r="11" spans="1:5">
+      <c r="A11" s="3" t="s">
         <v>22</v>
       </c>
-      <c r="E2" s="2">
+      <c r="B11" s="6">
+        <v>142.005</v>
+      </c>
+      <c r="C11" s="6">
+        <v>-86.3</v>
+      </c>
+      <c r="D11" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E11" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
-      <c r="A3" s="5" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="3">
-        <v>138.4</v>
-      </c>
-      <c r="C3" s="3">
-        <v>-102.35</v>
-      </c>
-      <c r="D3" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E3" s="3">
+    <row r="12" spans="1:5">
+      <c r="A12" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="B12" s="6">
+        <v>135.47</v>
+      </c>
+      <c r="C12" s="6">
+        <f>-129.07</f>
+        <v>-129.07</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E12" s="6">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="13" spans="1:5">
+      <c r="A13" s="3" t="s">
+        <v>12</v>
+      </c>
+      <c r="B13" s="6">
+        <v>126.3</v>
+      </c>
+      <c r="C13" s="6">
+        <v>-103.55</v>
+      </c>
+      <c r="D13" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E13" s="6">
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4" s="4" t="s">
-        <v>7</v>
-      </c>
-      <c r="B4" s="2">
-        <v>125.33750000000001</v>
-      </c>
-      <c r="C4" s="2">
-        <v>-112.47499999999999</v>
-      </c>
-      <c r="D4" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E4" s="2">
+    <row r="14" spans="1:5">
+      <c r="A14" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="6">
+        <v>128.02500000000001</v>
+      </c>
+      <c r="C14" s="6">
+        <v>-118.16249999999999</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E14" s="6">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="15" spans="1:5">
+      <c r="A15" s="3" t="s">
+        <v>23</v>
+      </c>
+      <c r="B15" s="6">
+        <v>142</v>
+      </c>
+      <c r="C15" s="6">
+        <v>-87.3</v>
+      </c>
+      <c r="D15" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E15" s="6">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="16" spans="1:5">
+      <c r="A16" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="B16" s="6">
+        <v>138.6</v>
+      </c>
+      <c r="C16" s="6">
+        <v>-94.8</v>
+      </c>
+      <c r="D16" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E16" s="6">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5">
+      <c r="A17" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B17" s="6">
+        <v>142.76750000000001</v>
+      </c>
+      <c r="C17" s="6">
+        <v>-109.75</v>
+      </c>
+      <c r="D17" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E17" s="6">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5">
+      <c r="A18" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="B18" s="6">
+        <v>129.875</v>
+      </c>
+      <c r="C18" s="6">
+        <v>-94.474999999999994</v>
+      </c>
+      <c r="D18" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E18" s="6">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5">
+      <c r="A19" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="B19" s="6">
+        <v>127.08750000000001</v>
+      </c>
+      <c r="C19" s="6">
+        <v>-109.71250000000001</v>
+      </c>
+      <c r="D19" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="E19" s="6">
         <v>-90</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
-      <c r="A5" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="B5" s="3">
-        <v>126.83750000000001</v>
-      </c>
-      <c r="C5" s="3">
-        <v>-112.47499999999999</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E5" s="3">
+    <row r="20" spans="1:5">
+      <c r="A20" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="B20" s="6">
+        <v>127.0625</v>
+      </c>
+      <c r="C20" s="6">
+        <v>-114.5625</v>
+      </c>
+      <c r="D20" s="4" t="s">
+        <v>19</v>
+      </c>
+      <c r="E20" s="6">
         <v>-90</v>
-      </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6" s="4" t="s">
-        <v>9</v>
-      </c>
-      <c r="B6" s="2">
-        <v>124.375</v>
-      </c>
-      <c r="C6" s="2">
-        <v>-101.33750000000001</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E6" s="2">
-        <v>-90</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7" s="5" t="s">
-        <v>10</v>
-      </c>
-      <c r="B7" s="3">
-        <v>129.32499999999999</v>
-      </c>
-      <c r="C7" s="3">
-        <v>-101.3125</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E7" s="3">
-        <v>-90</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5">
-      <c r="A8" s="4" t="s">
-        <v>20</v>
-      </c>
-      <c r="B8" s="2">
-        <v>128.33750000000001</v>
-      </c>
-      <c r="C8" s="2">
-        <v>-112.47499999999999</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E8" s="2">
-        <v>-90</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5">
-      <c r="A9" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="B9" s="3">
-        <v>129.3125</v>
-      </c>
-      <c r="C9" s="3">
-        <v>-106.175</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E9" s="3">
-        <v>-90</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5">
-      <c r="A10" s="4" t="s">
-        <v>24</v>
-      </c>
-      <c r="B10" s="2">
-        <v>124.33750000000001</v>
-      </c>
-      <c r="C10" s="2">
-        <v>-106.2</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E10" s="2">
-        <v>-90</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5">
-      <c r="A11" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="B11" s="3">
-        <v>142.005</v>
-      </c>
-      <c r="C11" s="3">
-        <v>-86.3</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E11" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5">
-      <c r="A12" s="4" t="s">
-        <v>11</v>
-      </c>
-      <c r="B12" s="2">
-        <v>132.81</v>
-      </c>
-      <c r="C12" s="2">
-        <v>-86.8</v>
-      </c>
-      <c r="D12" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E12" s="2">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5">
-      <c r="A13" s="5" t="s">
-        <v>12</v>
-      </c>
-      <c r="B13" s="3">
-        <v>135</v>
-      </c>
-      <c r="C13" s="3">
-        <v>-102.35</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E13" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="14" spans="1:5">
-      <c r="A14" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="2">
-        <v>130.47499999999999</v>
-      </c>
-      <c r="C14" s="2">
-        <v>-129.1</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E14" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5">
-      <c r="A15" s="5" t="s">
-        <v>14</v>
-      </c>
-      <c r="B15" s="3">
-        <v>127.15</v>
-      </c>
-      <c r="C15" s="3">
-        <v>-123.2</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E15" s="3">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="16" spans="1:5">
-      <c r="A16" s="4" t="s">
-        <v>21</v>
-      </c>
-      <c r="B16" s="2">
-        <v>145.55000000000001</v>
-      </c>
-      <c r="C16" s="2">
-        <v>-89.36</v>
-      </c>
-      <c r="D16" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E16" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="B17" s="3">
-        <v>135</v>
-      </c>
-      <c r="C17" s="3">
-        <v>-117.65</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E17" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="4" t="s">
-        <v>27</v>
-      </c>
-      <c r="B18" s="2">
-        <v>135</v>
-      </c>
-      <c r="C18" s="2">
-        <v>-108.1</v>
-      </c>
-      <c r="D18" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E18" s="2">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="B19" s="3">
-        <v>135</v>
-      </c>
-      <c r="C19" s="3">
-        <v>-111.9</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E19" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="4" t="s">
-        <v>15</v>
-      </c>
-      <c r="B20" s="2">
-        <v>127.8</v>
-      </c>
-      <c r="C20" s="2">
-        <v>-109.75</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E20" s="2">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="B21" s="3">
-        <v>142</v>
-      </c>
-      <c r="C21" s="3">
-        <v>-87.3</v>
-      </c>
-      <c r="D21" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E21" s="3">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="B22" s="2">
-        <v>138.6</v>
-      </c>
-      <c r="C22" s="2">
-        <v>-94.8</v>
-      </c>
-      <c r="D22" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E22" s="2">
-        <v>-90</v>
-      </c>
-    </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="5" t="s">
-        <v>17</v>
-      </c>
-      <c r="B23" s="3">
-        <v>142.76750000000001</v>
-      </c>
-      <c r="C23" s="3">
-        <v>-109.75</v>
-      </c>
-      <c r="D23" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E23" s="3">
-        <v>-90</v>
-      </c>
-    </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="B24" s="2">
-        <v>129.875</v>
-      </c>
-      <c r="C24" s="2">
-        <v>-94.474999999999994</v>
-      </c>
-      <c r="D24" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E24" s="2">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B25" s="3">
-        <v>126.8625</v>
-      </c>
-      <c r="C25" s="3">
-        <v>-101.3</v>
-      </c>
-      <c r="D25" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="E25" s="3">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="4" t="s">
-        <v>30</v>
-      </c>
-      <c r="B26" s="2">
-        <v>126.83750000000001</v>
-      </c>
-      <c r="C26" s="2">
-        <v>-106.15</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="E26" s="2">
-        <v>90</v>
       </c>
     </row>
   </sheetData>
